--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2038,6 +2038,1868 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125718596</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>504903</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7033183</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125719378</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80105</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>504808</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7033222</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125719690</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>504777</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7033263</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125719710</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58078</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>504790</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7033261</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125720370</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97208</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>504901</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7033129</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125721496</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>504817</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7032926</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125718617</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>504857</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7033231</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125719931</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91220</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>504834</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7033241</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125718899</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>504828</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7033245</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125720033</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58019</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>504891</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7033165</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125721476</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98347</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>504822</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7032914</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125720513</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>504904</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7033116</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125720107</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91238</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>504906</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7033144</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125719013</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>504824</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7033226</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125720078</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>504896</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7033159</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125719486</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>504815</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7033202</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125719843</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>504806</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7033267</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125720603</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97208</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Östersund, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>504891</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7033094</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125779085</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Öjsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>504767</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7032815</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2927,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125720033</v>
+        <v>125721476</v>
       </c>
       <c r="B23" t="n">
-        <v>58019</v>
+        <v>98347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504891</v>
+        <v>504822</v>
       </c>
       <c r="R23" t="n">
-        <v>7033165</v>
+        <v>7032914</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125721476</v>
+        <v>125720033</v>
       </c>
       <c r="B24" t="n">
-        <v>98347</v>
+        <v>58019</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,13 +3059,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504822</v>
+        <v>504891</v>
       </c>
       <c r="R24" t="n">
-        <v>7032914</v>
+        <v>7033165</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125720107</v>
+        <v>125719013</v>
       </c>
       <c r="B26" t="n">
-        <v>91238</v>
+        <v>80099</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504906</v>
+        <v>504824</v>
       </c>
       <c r="R26" t="n">
-        <v>7033144</v>
+        <v>7033226</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125719013</v>
+        <v>125720078</v>
       </c>
       <c r="B27" t="n">
-        <v>80099</v>
+        <v>98345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3326,21 +3326,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504824</v>
+        <v>504896</v>
       </c>
       <c r="R27" t="n">
-        <v>7033226</v>
+        <v>7033159</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125720078</v>
+        <v>125720107</v>
       </c>
       <c r="B28" t="n">
-        <v>98345</v>
+        <v>91238</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504896</v>
+        <v>504906</v>
       </c>
       <c r="R28" t="n">
-        <v>7033159</v>
+        <v>7033144</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2237,7 +2237,7 @@
         <v>125719690</v>
       </c>
       <c r="B16" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>125720370</v>
       </c>
       <c r="B18" t="n">
-        <v>97208</v>
+        <v>97215</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>125719931</v>
       </c>
       <c r="B21" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125721476</v>
+        <v>125720033</v>
       </c>
       <c r="B23" t="n">
-        <v>98347</v>
+        <v>58019</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504822</v>
+        <v>504891</v>
       </c>
       <c r="R23" t="n">
-        <v>7032914</v>
+        <v>7033165</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125720033</v>
+        <v>125721476</v>
       </c>
       <c r="B24" t="n">
-        <v>58019</v>
+        <v>98354</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,13 +3059,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504891</v>
+        <v>504822</v>
       </c>
       <c r="R24" t="n">
-        <v>7033165</v>
+        <v>7032914</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>125720513</v>
       </c>
       <c r="B25" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125720078</v>
+        <v>125720107</v>
       </c>
       <c r="B27" t="n">
-        <v>98345</v>
+        <v>91245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,13 +3350,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504896</v>
+        <v>504906</v>
       </c>
       <c r="R27" t="n">
-        <v>7033159</v>
+        <v>7033144</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125720107</v>
+        <v>125720078</v>
       </c>
       <c r="B28" t="n">
-        <v>91238</v>
+        <v>98352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504906</v>
+        <v>504896</v>
       </c>
       <c r="R28" t="n">
-        <v>7033144</v>
+        <v>7033159</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>125719843</v>
       </c>
       <c r="B30" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>125720603</v>
       </c>
       <c r="B31" t="n">
-        <v>97208</v>
+        <v>97215</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>125779085</v>
       </c>
       <c r="B32" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125719378</v>
+        <v>125719690</v>
       </c>
       <c r="B15" t="n">
-        <v>80105</v>
+        <v>98352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504808</v>
+        <v>504777</v>
       </c>
       <c r="R15" t="n">
-        <v>7033222</v>
+        <v>7033263</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125719690</v>
+        <v>125719378</v>
       </c>
       <c r="B16" t="n">
-        <v>98352</v>
+        <v>80105</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504777</v>
+        <v>504808</v>
       </c>
       <c r="R16" t="n">
-        <v>7033263</v>
+        <v>7033222</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125719690</v>
+        <v>125719378</v>
       </c>
       <c r="B15" t="n">
-        <v>98352</v>
+        <v>80105</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504777</v>
+        <v>504808</v>
       </c>
       <c r="R15" t="n">
-        <v>7033263</v>
+        <v>7033222</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125719378</v>
+        <v>125719690</v>
       </c>
       <c r="B16" t="n">
-        <v>80105</v>
+        <v>98352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504808</v>
+        <v>504777</v>
       </c>
       <c r="R16" t="n">
-        <v>7033222</v>
+        <v>7033263</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125719486</v>
+        <v>125719843</v>
       </c>
       <c r="B29" t="n">
-        <v>80099</v>
+        <v>98352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504815</v>
+        <v>504806</v>
       </c>
       <c r="R29" t="n">
-        <v>7033202</v>
+        <v>7033267</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125719843</v>
+        <v>125719486</v>
       </c>
       <c r="B30" t="n">
-        <v>98352</v>
+        <v>80099</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504806</v>
+        <v>504815</v>
       </c>
       <c r="R30" t="n">
-        <v>7033267</v>
+        <v>7033202</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2043,7 +2043,7 @@
         <v>125718596</v>
       </c>
       <c r="B14" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>125719378</v>
       </c>
       <c r="B15" t="n">
-        <v>80105</v>
+        <v>80106</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>125719690</v>
       </c>
       <c r="B16" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>125719710</v>
       </c>
       <c r="B17" t="n">
-        <v>58078</v>
+        <v>58079</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>125720370</v>
       </c>
       <c r="B18" t="n">
-        <v>97215</v>
+        <v>97218</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125721496</v>
+        <v>125718617</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>80072</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,21 +2545,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504817</v>
+        <v>504857</v>
       </c>
       <c r="R19" t="n">
-        <v>7032926</v>
+        <v>7033231</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2605,11 +2605,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2636,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718617</v>
+        <v>125721496</v>
       </c>
       <c r="B20" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,21 +2642,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2671,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504857</v>
+        <v>504817</v>
       </c>
       <c r="R20" t="n">
-        <v>7033231</v>
+        <v>7032926</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2707,6 +2702,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2736,7 +2736,7 @@
         <v>125719931</v>
       </c>
       <c r="B21" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>125718899</v>
       </c>
       <c r="B22" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125720033</v>
+        <v>125721476</v>
       </c>
       <c r="B23" t="n">
-        <v>58019</v>
+        <v>98357</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504891</v>
+        <v>504822</v>
       </c>
       <c r="R23" t="n">
-        <v>7033165</v>
+        <v>7032914</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125721476</v>
+        <v>125720033</v>
       </c>
       <c r="B24" t="n">
-        <v>98354</v>
+        <v>58020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,13 +3059,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504822</v>
+        <v>504891</v>
       </c>
       <c r="R24" t="n">
-        <v>7032914</v>
+        <v>7033165</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>125720513</v>
       </c>
       <c r="B25" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>125719013</v>
       </c>
       <c r="B26" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>125720107</v>
       </c>
       <c r="B27" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>125720078</v>
       </c>
       <c r="B28" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125719843</v>
+        <v>125719486</v>
       </c>
       <c r="B29" t="n">
-        <v>98352</v>
+        <v>80100</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504806</v>
+        <v>504815</v>
       </c>
       <c r="R29" t="n">
-        <v>7033267</v>
+        <v>7033202</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125719486</v>
+        <v>125719843</v>
       </c>
       <c r="B30" t="n">
-        <v>80099</v>
+        <v>98355</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504815</v>
+        <v>504806</v>
       </c>
       <c r="R30" t="n">
-        <v>7033202</v>
+        <v>7033267</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>125720603</v>
       </c>
       <c r="B31" t="n">
-        <v>97215</v>
+        <v>97218</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>125779085</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -3218,32 +3218,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125719013</v>
+        <v>125720107</v>
       </c>
       <c r="B26" t="n">
-        <v>80100</v>
+        <v>91246</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504824</v>
+        <v>504906</v>
       </c>
       <c r="R26" t="n">
-        <v>7033226</v>
+        <v>7033144</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125720107</v>
+        <v>125719013</v>
       </c>
       <c r="B27" t="n">
-        <v>91246</v>
+        <v>80100</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,13 +3350,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504906</v>
+        <v>504824</v>
       </c>
       <c r="R27" t="n">
-        <v>7033144</v>
+        <v>7033226</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125719486</v>
+        <v>125719843</v>
       </c>
       <c r="B29" t="n">
-        <v>80100</v>
+        <v>98355</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504815</v>
+        <v>504806</v>
       </c>
       <c r="R29" t="n">
-        <v>7033202</v>
+        <v>7033267</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125719843</v>
+        <v>125719486</v>
       </c>
       <c r="B30" t="n">
-        <v>98355</v>
+        <v>80100</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504806</v>
+        <v>504815</v>
       </c>
       <c r="R30" t="n">
-        <v>7033267</v>
+        <v>7033202</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2043,7 +2043,7 @@
         <v>125718596</v>
       </c>
       <c r="B14" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125719378</v>
+        <v>125719690</v>
       </c>
       <c r="B15" t="n">
-        <v>80106</v>
+        <v>98359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504808</v>
+        <v>504777</v>
       </c>
       <c r="R15" t="n">
-        <v>7033222</v>
+        <v>7033263</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125719690</v>
+        <v>125719378</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>80110</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504777</v>
+        <v>504808</v>
       </c>
       <c r="R16" t="n">
-        <v>7033263</v>
+        <v>7033222</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2437,32 +2437,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125720370</v>
+        <v>125721496</v>
       </c>
       <c r="B18" t="n">
-        <v>97218</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504901</v>
+        <v>504817</v>
       </c>
       <c r="R18" t="n">
-        <v>7033129</v>
+        <v>7032926</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2508,6 +2508,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,32 +2539,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125718617</v>
+        <v>125720370</v>
       </c>
       <c r="B19" t="n">
-        <v>80072</v>
+        <v>97222</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,10 +2574,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504857</v>
+        <v>504901</v>
       </c>
       <c r="R19" t="n">
-        <v>7033231</v>
+        <v>7033129</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2631,10 +2636,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125721496</v>
+        <v>125718617</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>80076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,21 +2647,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2666,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504817</v>
+        <v>504857</v>
       </c>
       <c r="R20" t="n">
-        <v>7032926</v>
+        <v>7033231</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2702,11 +2707,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2736,7 +2736,7 @@
         <v>125719931</v>
       </c>
       <c r="B21" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>125718899</v>
       </c>
       <c r="B22" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125721476</v>
+        <v>125720033</v>
       </c>
       <c r="B23" t="n">
-        <v>98357</v>
+        <v>58020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504822</v>
+        <v>504891</v>
       </c>
       <c r="R23" t="n">
-        <v>7032914</v>
+        <v>7033165</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125720033</v>
+        <v>125721476</v>
       </c>
       <c r="B24" t="n">
-        <v>58020</v>
+        <v>98361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,13 +3059,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504891</v>
+        <v>504822</v>
       </c>
       <c r="R24" t="n">
-        <v>7033165</v>
+        <v>7032914</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>125720513</v>
       </c>
       <c r="B25" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125720107</v>
+        <v>125720078</v>
       </c>
       <c r="B26" t="n">
-        <v>91246</v>
+        <v>98359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504906</v>
+        <v>504896</v>
       </c>
       <c r="R26" t="n">
-        <v>7033144</v>
+        <v>7033159</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125719013</v>
+        <v>125720107</v>
       </c>
       <c r="B27" t="n">
-        <v>80100</v>
+        <v>91250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,13 +3350,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504824</v>
+        <v>504906</v>
       </c>
       <c r="R27" t="n">
-        <v>7033226</v>
+        <v>7033144</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125720078</v>
+        <v>125719013</v>
       </c>
       <c r="B28" t="n">
-        <v>98355</v>
+        <v>80104</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504896</v>
+        <v>504824</v>
       </c>
       <c r="R28" t="n">
-        <v>7033159</v>
+        <v>7033226</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3512,7 +3512,7 @@
         <v>125719843</v>
       </c>
       <c r="B29" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>125719486</v>
       </c>
       <c r="B30" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>125720603</v>
       </c>
       <c r="B31" t="n">
-        <v>97218</v>
+        <v>97222</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>125779085</v>
       </c>
       <c r="B32" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2539,32 +2539,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125720370</v>
+        <v>125718617</v>
       </c>
       <c r="B19" t="n">
-        <v>97222</v>
+        <v>80076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504901</v>
+        <v>504857</v>
       </c>
       <c r="R19" t="n">
-        <v>7033129</v>
+        <v>7033231</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2636,32 +2636,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718617</v>
+        <v>125720370</v>
       </c>
       <c r="B20" t="n">
-        <v>80076</v>
+        <v>97222</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504857</v>
+        <v>504901</v>
       </c>
       <c r="R20" t="n">
-        <v>7033231</v>
+        <v>7033129</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125720033</v>
+        <v>125721476</v>
       </c>
       <c r="B23" t="n">
-        <v>58020</v>
+        <v>98361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504891</v>
+        <v>504822</v>
       </c>
       <c r="R23" t="n">
-        <v>7033165</v>
+        <v>7032914</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125721476</v>
+        <v>125720033</v>
       </c>
       <c r="B24" t="n">
-        <v>98361</v>
+        <v>58020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,13 +3059,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504822</v>
+        <v>504891</v>
       </c>
       <c r="R24" t="n">
-        <v>7032914</v>
+        <v>7033165</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125719843</v>
+        <v>125719486</v>
       </c>
       <c r="B29" t="n">
-        <v>98359</v>
+        <v>80104</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504806</v>
+        <v>504815</v>
       </c>
       <c r="R29" t="n">
-        <v>7033267</v>
+        <v>7033202</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125719486</v>
+        <v>125719843</v>
       </c>
       <c r="B30" t="n">
-        <v>80104</v>
+        <v>98359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504815</v>
+        <v>504806</v>
       </c>
       <c r="R30" t="n">
-        <v>7033202</v>
+        <v>7033267</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2140,7 +2140,7 @@
         <v>125719690</v>
       </c>
       <c r="B15" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2539,32 +2539,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125718617</v>
+        <v>125720370</v>
       </c>
       <c r="B19" t="n">
-        <v>80076</v>
+        <v>97223</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504857</v>
+        <v>504901</v>
       </c>
       <c r="R19" t="n">
-        <v>7033231</v>
+        <v>7033129</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2636,32 +2636,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125720370</v>
+        <v>125718617</v>
       </c>
       <c r="B20" t="n">
-        <v>97222</v>
+        <v>80076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504901</v>
+        <v>504857</v>
       </c>
       <c r="R20" t="n">
-        <v>7033129</v>
+        <v>7033231</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2930,7 +2930,7 @@
         <v>125721476</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>125720513</v>
       </c>
       <c r="B25" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125720078</v>
+        <v>125719013</v>
       </c>
       <c r="B26" t="n">
-        <v>98359</v>
+        <v>80104</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,21 +3229,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504896</v>
+        <v>504824</v>
       </c>
       <c r="R26" t="n">
-        <v>7033159</v>
+        <v>7033226</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125719013</v>
+        <v>125720078</v>
       </c>
       <c r="B28" t="n">
-        <v>80104</v>
+        <v>98360</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504824</v>
+        <v>504896</v>
       </c>
       <c r="R28" t="n">
-        <v>7033226</v>
+        <v>7033159</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3609,7 +3609,7 @@
         <v>125719843</v>
       </c>
       <c r="B30" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>125720603</v>
       </c>
       <c r="B31" t="n">
-        <v>97222</v>
+        <v>97223</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>125779085</v>
       </c>
       <c r="B32" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125719690</v>
+        <v>125719378</v>
       </c>
       <c r="B15" t="n">
-        <v>98360</v>
+        <v>80110</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504777</v>
+        <v>504808</v>
       </c>
       <c r="R15" t="n">
-        <v>7033263</v>
+        <v>7033222</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125719378</v>
+        <v>125719690</v>
       </c>
       <c r="B16" t="n">
-        <v>80110</v>
+        <v>98360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504808</v>
+        <v>504777</v>
       </c>
       <c r="R16" t="n">
-        <v>7033222</v>
+        <v>7033263</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2437,32 +2437,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125721496</v>
+        <v>125720370</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>97223</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504817</v>
+        <v>504901</v>
       </c>
       <c r="R18" t="n">
-        <v>7032926</v>
+        <v>7033129</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2508,11 +2508,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,32 +2534,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125720370</v>
+        <v>125721496</v>
       </c>
       <c r="B19" t="n">
-        <v>97223</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2574,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504901</v>
+        <v>504817</v>
       </c>
       <c r="R19" t="n">
-        <v>7033129</v>
+        <v>7032926</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2610,6 +2605,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2927,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125721476</v>
+        <v>125720033</v>
       </c>
       <c r="B23" t="n">
-        <v>98362</v>
+        <v>58020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504822</v>
+        <v>504891</v>
       </c>
       <c r="R23" t="n">
-        <v>7032914</v>
+        <v>7033165</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125720033</v>
+        <v>125721476</v>
       </c>
       <c r="B24" t="n">
-        <v>58020</v>
+        <v>98362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,13 +3059,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504891</v>
+        <v>504822</v>
       </c>
       <c r="R24" t="n">
-        <v>7033165</v>
+        <v>7032914</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125719013</v>
+        <v>125720078</v>
       </c>
       <c r="B26" t="n">
-        <v>80104</v>
+        <v>98360</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,21 +3229,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504824</v>
+        <v>504896</v>
       </c>
       <c r="R26" t="n">
-        <v>7033226</v>
+        <v>7033159</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125720107</v>
+        <v>125719013</v>
       </c>
       <c r="B27" t="n">
-        <v>91250</v>
+        <v>80104</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,13 +3350,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504906</v>
+        <v>504824</v>
       </c>
       <c r="R27" t="n">
-        <v>7033144</v>
+        <v>7033226</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125720078</v>
+        <v>125720107</v>
       </c>
       <c r="B28" t="n">
-        <v>98360</v>
+        <v>91250</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504896</v>
+        <v>504906</v>
       </c>
       <c r="R28" t="n">
-        <v>7033159</v>
+        <v>7033144</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125719378</v>
+        <v>125719690</v>
       </c>
       <c r="B15" t="n">
-        <v>80110</v>
+        <v>98360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504808</v>
+        <v>504777</v>
       </c>
       <c r="R15" t="n">
-        <v>7033222</v>
+        <v>7033263</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125719690</v>
+        <v>125719378</v>
       </c>
       <c r="B16" t="n">
-        <v>98360</v>
+        <v>80110</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504777</v>
+        <v>504808</v>
       </c>
       <c r="R16" t="n">
-        <v>7033263</v>
+        <v>7033222</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2437,32 +2437,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125720370</v>
+        <v>125721496</v>
       </c>
       <c r="B18" t="n">
-        <v>97223</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504901</v>
+        <v>504817</v>
       </c>
       <c r="R18" t="n">
-        <v>7033129</v>
+        <v>7032926</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2508,6 +2508,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,32 +2539,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125721496</v>
+        <v>125720370</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>97223</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,10 +2574,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504817</v>
+        <v>504901</v>
       </c>
       <c r="R19" t="n">
-        <v>7032926</v>
+        <v>7033129</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2605,11 +2610,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2927,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125720033</v>
+        <v>125721476</v>
       </c>
       <c r="B23" t="n">
-        <v>58020</v>
+        <v>98362</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504891</v>
+        <v>504822</v>
       </c>
       <c r="R23" t="n">
-        <v>7033165</v>
+        <v>7032914</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125721476</v>
+        <v>125720033</v>
       </c>
       <c r="B24" t="n">
-        <v>98362</v>
+        <v>58020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,13 +3059,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504822</v>
+        <v>504891</v>
       </c>
       <c r="R24" t="n">
-        <v>7032914</v>
+        <v>7033165</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125720078</v>
+        <v>125719013</v>
       </c>
       <c r="B26" t="n">
-        <v>98360</v>
+        <v>80104</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,21 +3229,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504896</v>
+        <v>504824</v>
       </c>
       <c r="R26" t="n">
-        <v>7033159</v>
+        <v>7033226</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125719013</v>
+        <v>125720107</v>
       </c>
       <c r="B27" t="n">
-        <v>80104</v>
+        <v>91250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,13 +3350,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504824</v>
+        <v>504906</v>
       </c>
       <c r="R27" t="n">
-        <v>7033226</v>
+        <v>7033144</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125720107</v>
+        <v>125720078</v>
       </c>
       <c r="B28" t="n">
-        <v>91250</v>
+        <v>98360</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504906</v>
+        <v>504896</v>
       </c>
       <c r="R28" t="n">
-        <v>7033144</v>
+        <v>7033159</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2043,7 +2043,7 @@
         <v>125718596</v>
       </c>
       <c r="B14" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>125719690</v>
       </c>
       <c r="B15" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>125719378</v>
       </c>
       <c r="B16" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>125719710</v>
       </c>
       <c r="B17" t="n">
-        <v>58079</v>
+        <v>58080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>125721496</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2539,32 +2539,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125720370</v>
+        <v>125718617</v>
       </c>
       <c r="B19" t="n">
-        <v>97223</v>
+        <v>80077</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504901</v>
+        <v>504857</v>
       </c>
       <c r="R19" t="n">
-        <v>7033129</v>
+        <v>7033231</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2636,32 +2636,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718617</v>
+        <v>125720370</v>
       </c>
       <c r="B20" t="n">
-        <v>80076</v>
+        <v>97225</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504857</v>
+        <v>504901</v>
       </c>
       <c r="R20" t="n">
-        <v>7033231</v>
+        <v>7033129</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2736,7 +2736,7 @@
         <v>125719931</v>
       </c>
       <c r="B21" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>125718899</v>
       </c>
       <c r="B22" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125721476</v>
+        <v>125720033</v>
       </c>
       <c r="B23" t="n">
-        <v>98362</v>
+        <v>58021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504822</v>
+        <v>504891</v>
       </c>
       <c r="R23" t="n">
-        <v>7032914</v>
+        <v>7033165</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125720033</v>
+        <v>125721476</v>
       </c>
       <c r="B24" t="n">
-        <v>58020</v>
+        <v>98364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,13 +3059,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504891</v>
+        <v>504822</v>
       </c>
       <c r="R24" t="n">
-        <v>7033165</v>
+        <v>7032914</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>125720513</v>
       </c>
       <c r="B25" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125719013</v>
+        <v>125720078</v>
       </c>
       <c r="B26" t="n">
-        <v>80104</v>
+        <v>98362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,21 +3229,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504824</v>
+        <v>504896</v>
       </c>
       <c r="R26" t="n">
-        <v>7033226</v>
+        <v>7033159</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125720107</v>
+        <v>125719013</v>
       </c>
       <c r="B27" t="n">
-        <v>91250</v>
+        <v>80105</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,13 +3350,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504906</v>
+        <v>504824</v>
       </c>
       <c r="R27" t="n">
-        <v>7033144</v>
+        <v>7033226</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125720078</v>
+        <v>125720107</v>
       </c>
       <c r="B28" t="n">
-        <v>98360</v>
+        <v>91252</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504896</v>
+        <v>504906</v>
       </c>
       <c r="R28" t="n">
-        <v>7033159</v>
+        <v>7033144</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125719486</v>
+        <v>125719843</v>
       </c>
       <c r="B29" t="n">
-        <v>80104</v>
+        <v>98362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504815</v>
+        <v>504806</v>
       </c>
       <c r="R29" t="n">
-        <v>7033202</v>
+        <v>7033267</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125719843</v>
+        <v>125719486</v>
       </c>
       <c r="B30" t="n">
-        <v>98360</v>
+        <v>80105</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504806</v>
+        <v>504815</v>
       </c>
       <c r="R30" t="n">
-        <v>7033267</v>
+        <v>7033202</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>125720603</v>
       </c>
       <c r="B31" t="n">
-        <v>97223</v>
+        <v>97225</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>125779085</v>
       </c>
       <c r="B32" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125719690</v>
+        <v>125719378</v>
       </c>
       <c r="B15" t="n">
-        <v>98362</v>
+        <v>80111</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504777</v>
+        <v>504808</v>
       </c>
       <c r="R15" t="n">
-        <v>7033263</v>
+        <v>7033222</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125719378</v>
+        <v>125719690</v>
       </c>
       <c r="B16" t="n">
-        <v>80111</v>
+        <v>98362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504808</v>
+        <v>504777</v>
       </c>
       <c r="R16" t="n">
-        <v>7033222</v>
+        <v>7033263</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125719378</v>
+        <v>125719690</v>
       </c>
       <c r="B15" t="n">
-        <v>80111</v>
+        <v>98364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504808</v>
+        <v>504777</v>
       </c>
       <c r="R15" t="n">
-        <v>7033222</v>
+        <v>7033263</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125719690</v>
+        <v>125719378</v>
       </c>
       <c r="B16" t="n">
-        <v>98362</v>
+        <v>80111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504777</v>
+        <v>504808</v>
       </c>
       <c r="R16" t="n">
-        <v>7033263</v>
+        <v>7033222</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2639,7 +2639,7 @@
         <v>125720370</v>
       </c>
       <c r="B20" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>125719931</v>
       </c>
       <c r="B21" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>125721476</v>
       </c>
       <c r="B24" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>125720513</v>
       </c>
       <c r="B25" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125720078</v>
+        <v>125719013</v>
       </c>
       <c r="B26" t="n">
-        <v>98362</v>
+        <v>80105</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,21 +3229,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504896</v>
+        <v>504824</v>
       </c>
       <c r="R26" t="n">
-        <v>7033159</v>
+        <v>7033226</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125719013</v>
+        <v>125720078</v>
       </c>
       <c r="B27" t="n">
-        <v>80105</v>
+        <v>98364</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3326,21 +3326,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504824</v>
+        <v>504896</v>
       </c>
       <c r="R27" t="n">
-        <v>7033226</v>
+        <v>7033159</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3415,7 +3415,7 @@
         <v>125720107</v>
       </c>
       <c r="B28" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125719843</v>
+        <v>125719486</v>
       </c>
       <c r="B29" t="n">
-        <v>98362</v>
+        <v>80105</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504806</v>
+        <v>504815</v>
       </c>
       <c r="R29" t="n">
-        <v>7033267</v>
+        <v>7033202</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125719486</v>
+        <v>125719843</v>
       </c>
       <c r="B30" t="n">
-        <v>80105</v>
+        <v>98364</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504815</v>
+        <v>504806</v>
       </c>
       <c r="R30" t="n">
-        <v>7033202</v>
+        <v>7033267</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>125720603</v>
       </c>
       <c r="B31" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>125779085</v>
       </c>
       <c r="B32" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125719690</v>
+        <v>125719378</v>
       </c>
       <c r="B15" t="n">
-        <v>98364</v>
+        <v>80111</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504777</v>
+        <v>504808</v>
       </c>
       <c r="R15" t="n">
-        <v>7033263</v>
+        <v>7033222</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125719378</v>
+        <v>125719690</v>
       </c>
       <c r="B16" t="n">
-        <v>80111</v>
+        <v>98364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504808</v>
+        <v>504777</v>
       </c>
       <c r="R16" t="n">
-        <v>7033222</v>
+        <v>7033263</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125719013</v>
+        <v>125720078</v>
       </c>
       <c r="B26" t="n">
-        <v>80105</v>
+        <v>98364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,21 +3229,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504824</v>
+        <v>504896</v>
       </c>
       <c r="R26" t="n">
-        <v>7033226</v>
+        <v>7033159</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125720078</v>
+        <v>125720107</v>
       </c>
       <c r="B27" t="n">
-        <v>98364</v>
+        <v>91254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,13 +3350,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504896</v>
+        <v>504906</v>
       </c>
       <c r="R27" t="n">
-        <v>7033159</v>
+        <v>7033144</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125720107</v>
+        <v>125719013</v>
       </c>
       <c r="B28" t="n">
-        <v>91254</v>
+        <v>80105</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504906</v>
+        <v>504824</v>
       </c>
       <c r="R28" t="n">
-        <v>7033144</v>
+        <v>7033226</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2237,7 +2237,7 @@
         <v>125719690</v>
       </c>
       <c r="B16" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125721496</v>
+        <v>125718617</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,21 +2448,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504817</v>
+        <v>504857</v>
       </c>
       <c r="R18" t="n">
-        <v>7032926</v>
+        <v>7033231</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2508,11 +2508,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125718617</v>
+        <v>125721496</v>
       </c>
       <c r="B19" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2550,21 +2545,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2574,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504857</v>
+        <v>504817</v>
       </c>
       <c r="R19" t="n">
-        <v>7033231</v>
+        <v>7032926</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2610,6 +2605,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2639,7 +2639,7 @@
         <v>125720370</v>
       </c>
       <c r="B20" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>125719931</v>
       </c>
       <c r="B21" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>125721476</v>
       </c>
       <c r="B24" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>125720513</v>
       </c>
       <c r="B25" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125720078</v>
+        <v>125719013</v>
       </c>
       <c r="B26" t="n">
-        <v>98364</v>
+        <v>80105</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,21 +3229,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504896</v>
+        <v>504824</v>
       </c>
       <c r="R26" t="n">
-        <v>7033159</v>
+        <v>7033226</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125720107</v>
+        <v>125720078</v>
       </c>
       <c r="B27" t="n">
-        <v>91254</v>
+        <v>98366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,13 +3350,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504906</v>
+        <v>504896</v>
       </c>
       <c r="R27" t="n">
-        <v>7033144</v>
+        <v>7033159</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125719013</v>
+        <v>125720107</v>
       </c>
       <c r="B28" t="n">
-        <v>80105</v>
+        <v>91256</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504824</v>
+        <v>504906</v>
       </c>
       <c r="R28" t="n">
-        <v>7033226</v>
+        <v>7033144</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>125719843</v>
       </c>
       <c r="B30" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>125720603</v>
       </c>
       <c r="B31" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>125779085</v>
       </c>
       <c r="B32" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -3509,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125719486</v>
+        <v>125719843</v>
       </c>
       <c r="B29" t="n">
-        <v>80105</v>
+        <v>98366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504815</v>
+        <v>504806</v>
       </c>
       <c r="R29" t="n">
-        <v>7033202</v>
+        <v>7033267</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125719843</v>
+        <v>125719486</v>
       </c>
       <c r="B30" t="n">
-        <v>98366</v>
+        <v>80105</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504806</v>
+        <v>504815</v>
       </c>
       <c r="R30" t="n">
-        <v>7033267</v>
+        <v>7033202</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2043,7 +2043,7 @@
         <v>125718596</v>
       </c>
       <c r="B14" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125719378</v>
+        <v>125719690</v>
       </c>
       <c r="B15" t="n">
-        <v>80111</v>
+        <v>98370</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504808</v>
+        <v>504777</v>
       </c>
       <c r="R15" t="n">
-        <v>7033222</v>
+        <v>7033263</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125719690</v>
+        <v>125719378</v>
       </c>
       <c r="B16" t="n">
-        <v>98366</v>
+        <v>80115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504777</v>
+        <v>504808</v>
       </c>
       <c r="R16" t="n">
-        <v>7033263</v>
+        <v>7033222</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2334,7 +2334,7 @@
         <v>125719710</v>
       </c>
       <c r="B17" t="n">
-        <v>58080</v>
+        <v>58084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125718617</v>
+        <v>125721496</v>
       </c>
       <c r="B18" t="n">
-        <v>80077</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,21 +2448,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504857</v>
+        <v>504817</v>
       </c>
       <c r="R18" t="n">
-        <v>7033231</v>
+        <v>7032926</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2508,6 +2508,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,32 +2539,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125721496</v>
+        <v>125720370</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>97233</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,10 +2574,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504817</v>
+        <v>504901</v>
       </c>
       <c r="R19" t="n">
-        <v>7032926</v>
+        <v>7033129</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2605,11 +2610,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2636,32 +2636,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125720370</v>
+        <v>125718617</v>
       </c>
       <c r="B20" t="n">
-        <v>97229</v>
+        <v>80081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504901</v>
+        <v>504857</v>
       </c>
       <c r="R20" t="n">
-        <v>7033129</v>
+        <v>7033231</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2736,7 +2736,7 @@
         <v>125719931</v>
       </c>
       <c r="B21" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>125718899</v>
       </c>
       <c r="B22" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>125720033</v>
       </c>
       <c r="B23" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>125721476</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>125720513</v>
       </c>
       <c r="B25" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125719013</v>
+        <v>125720107</v>
       </c>
       <c r="B26" t="n">
-        <v>80105</v>
+        <v>91260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504824</v>
+        <v>504906</v>
       </c>
       <c r="R26" t="n">
-        <v>7033226</v>
+        <v>7033144</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125720078</v>
+        <v>125719013</v>
       </c>
       <c r="B27" t="n">
-        <v>98366</v>
+        <v>80109</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3326,21 +3326,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504896</v>
+        <v>504824</v>
       </c>
       <c r="R27" t="n">
-        <v>7033159</v>
+        <v>7033226</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125720107</v>
+        <v>125720078</v>
       </c>
       <c r="B28" t="n">
-        <v>91256</v>
+        <v>98370</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504906</v>
+        <v>504896</v>
       </c>
       <c r="R28" t="n">
-        <v>7033144</v>
+        <v>7033159</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125719843</v>
+        <v>125719486</v>
       </c>
       <c r="B29" t="n">
-        <v>98366</v>
+        <v>80109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504806</v>
+        <v>504815</v>
       </c>
       <c r="R29" t="n">
-        <v>7033267</v>
+        <v>7033202</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125719486</v>
+        <v>125719843</v>
       </c>
       <c r="B30" t="n">
-        <v>80105</v>
+        <v>98370</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504815</v>
+        <v>504806</v>
       </c>
       <c r="R30" t="n">
-        <v>7033202</v>
+        <v>7033267</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>125720603</v>
       </c>
       <c r="B31" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>125779085</v>
       </c>
       <c r="B32" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125719690</v>
+        <v>125719378</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>80115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504777</v>
+        <v>504808</v>
       </c>
       <c r="R15" t="n">
-        <v>7033263</v>
+        <v>7033222</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125719378</v>
+        <v>125719690</v>
       </c>
       <c r="B16" t="n">
-        <v>80115</v>
+        <v>98370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504808</v>
+        <v>504777</v>
       </c>
       <c r="R16" t="n">
-        <v>7033222</v>
+        <v>7033263</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125721496</v>
+        <v>125718617</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,21 +2448,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504817</v>
+        <v>504857</v>
       </c>
       <c r="R18" t="n">
-        <v>7032926</v>
+        <v>7033231</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2508,11 +2508,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,32 +2534,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125720370</v>
+        <v>125721496</v>
       </c>
       <c r="B19" t="n">
-        <v>97233</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2574,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504901</v>
+        <v>504817</v>
       </c>
       <c r="R19" t="n">
-        <v>7033129</v>
+        <v>7032926</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2610,6 +2605,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2636,32 +2636,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718617</v>
+        <v>125720370</v>
       </c>
       <c r="B20" t="n">
-        <v>80081</v>
+        <v>97233</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504857</v>
+        <v>504901</v>
       </c>
       <c r="R20" t="n">
-        <v>7033231</v>
+        <v>7033129</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125719378</v>
+        <v>125719690</v>
       </c>
       <c r="B15" t="n">
-        <v>80115</v>
+        <v>98373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504808</v>
+        <v>504777</v>
       </c>
       <c r="R15" t="n">
-        <v>7033222</v>
+        <v>7033263</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125719690</v>
+        <v>125719378</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>80115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504777</v>
+        <v>504808</v>
       </c>
       <c r="R16" t="n">
-        <v>7033263</v>
+        <v>7033222</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2639,7 +2639,7 @@
         <v>125720370</v>
       </c>
       <c r="B20" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125720033</v>
+        <v>125721476</v>
       </c>
       <c r="B23" t="n">
-        <v>58025</v>
+        <v>98375</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504891</v>
+        <v>504822</v>
       </c>
       <c r="R23" t="n">
-        <v>7033165</v>
+        <v>7032914</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125721476</v>
+        <v>125720033</v>
       </c>
       <c r="B24" t="n">
-        <v>98372</v>
+        <v>58025</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,13 +3059,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504822</v>
+        <v>504891</v>
       </c>
       <c r="R24" t="n">
-        <v>7032914</v>
+        <v>7033165</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>125720513</v>
       </c>
       <c r="B25" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125720107</v>
+        <v>125720078</v>
       </c>
       <c r="B26" t="n">
-        <v>91260</v>
+        <v>98373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504906</v>
+        <v>504896</v>
       </c>
       <c r="R26" t="n">
-        <v>7033144</v>
+        <v>7033159</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125720078</v>
+        <v>125720107</v>
       </c>
       <c r="B28" t="n">
-        <v>98370</v>
+        <v>91260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504896</v>
+        <v>504906</v>
       </c>
       <c r="R28" t="n">
-        <v>7033159</v>
+        <v>7033144</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>125719843</v>
       </c>
       <c r="B30" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>125720603</v>
       </c>
       <c r="B31" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>125779085</v>
       </c>
       <c r="B32" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 2237-2022 artfynd.xlsx
+++ b/artfynd/A 2237-2022 artfynd.xlsx
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125719690</v>
+        <v>125719378</v>
       </c>
       <c r="B15" t="n">
-        <v>98373</v>
+        <v>80115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504777</v>
+        <v>504808</v>
       </c>
       <c r="R15" t="n">
-        <v>7033263</v>
+        <v>7033222</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125719378</v>
+        <v>125719690</v>
       </c>
       <c r="B16" t="n">
-        <v>80115</v>
+        <v>98373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504808</v>
+        <v>504777</v>
       </c>
       <c r="R16" t="n">
-        <v>7033222</v>
+        <v>7033263</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125720078</v>
+        <v>125720107</v>
       </c>
       <c r="B26" t="n">
-        <v>98373</v>
+        <v>91260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504896</v>
+        <v>504906</v>
       </c>
       <c r="R26" t="n">
-        <v>7033159</v>
+        <v>7033144</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125720107</v>
+        <v>125720078</v>
       </c>
       <c r="B28" t="n">
-        <v>91260</v>
+        <v>98373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504906</v>
+        <v>504896</v>
       </c>
       <c r="R28" t="n">
-        <v>7033144</v>
+        <v>7033159</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
